--- a/PaintShop-September2026.xlsx
+++ b/PaintShop-September2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stichtingfontys.sharepoint.com/sites/TW-or/Gedeelde documenten/or/2026-2027/Jaar 2/OR5 - Improving Search/exam/assignment Paint Shop/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stichtingfontys-my.sharepoint.com/personal/582755_student_fontys_nl/Documents/Leerjaar 2/Periode 1/Operations Research 5/OR5/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="90" documentId="11_3C5A325E12D14DD35BD44A2F14D57A2270643C57" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50D7B682-22B1-4A93-AE84-3591F3F49460}"/>
+  <xr:revisionPtr revIDLastSave="94" documentId="11_3C5A325E12D14DD35BD44A2F14D57A2270643C57" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F4FAE6A-01B5-47AE-8C9A-AC22BD9F2601}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="0" windowWidth="14610" windowHeight="15585" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1800" yWindow="1290" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Orders" sheetId="1" r:id="rId1"/>
@@ -206,7 +206,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -229,11 +229,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -260,9 +271,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -541,16 +558,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E29"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.5546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.33203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.28515625" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="30" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>5</v>
       </c>
@@ -567,7 +584,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="30" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>17</v>
       </c>
@@ -584,7 +601,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>18</v>
       </c>
@@ -601,7 +618,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>19</v>
       </c>
@@ -618,7 +635,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="30" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>20</v>
       </c>
@@ -635,7 +652,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="30" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>21</v>
       </c>
@@ -652,7 +669,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" ht="30" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>22</v>
       </c>
@@ -669,7 +686,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="30" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>23</v>
       </c>
@@ -686,7 +703,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="30" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>24</v>
       </c>
@@ -703,7 +720,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="30" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>25</v>
       </c>
@@ -720,7 +737,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="30" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>26</v>
       </c>
@@ -737,7 +754,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" ht="30" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>27</v>
       </c>
@@ -754,7 +771,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" ht="30" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
         <v>28</v>
       </c>
@@ -771,7 +788,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" ht="30" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
         <v>29</v>
       </c>
@@ -788,7 +805,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" ht="30" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>30</v>
       </c>
@@ -805,7 +822,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" ht="30" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
         <v>31</v>
       </c>
@@ -822,7 +839,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" ht="30" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
         <v>32</v>
       </c>
@@ -839,7 +856,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" ht="30" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
         <v>33</v>
       </c>
@@ -856,7 +873,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" ht="30" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
         <v>34</v>
       </c>
@@ -873,7 +890,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" ht="30" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
         <v>35</v>
       </c>
@@ -890,7 +907,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" ht="30" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
         <v>36</v>
       </c>
@@ -907,7 +924,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" ht="30" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
         <v>37</v>
       </c>
@@ -924,7 +941,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" ht="30" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
         <v>38</v>
       </c>
@@ -941,7 +958,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" ht="30" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
         <v>39</v>
       </c>
@@ -958,7 +975,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" ht="30" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
         <v>40</v>
       </c>
@@ -975,7 +992,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" ht="30" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
         <v>41</v>
       </c>
@@ -992,7 +1009,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" ht="30" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
         <v>42</v>
       </c>
@@ -1009,7 +1026,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" ht="30" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
         <v>43</v>
       </c>
@@ -1026,7 +1043,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" ht="30" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
         <v>44</v>
       </c>
@@ -1051,14 +1068,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.77734375" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.7109375" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="30" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1066,7 +1083,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -1074,7 +1091,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -1082,13 +1099,17 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="8">
         <v>18</v>
       </c>
+    </row>
+    <row r="5" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A5" s="10"/>
+      <c r="B5" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1098,14 +1119,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>15</v>
       </c>
@@ -1116,7 +1137,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -1127,7 +1148,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -1138,7 +1159,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -1149,7 +1170,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -1160,7 +1181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -1171,7 +1192,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
@@ -1182,7 +1203,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
@@ -1193,7 +1214,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
@@ -1204,7 +1225,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
@@ -1215,7 +1236,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1226,7 +1247,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1237,7 +1258,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>8</v>
       </c>
